--- a/artfynd/A 12338-2025 artfynd.xlsx
+++ b/artfynd/A 12338-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74250299</v>
+        <v>93943789</v>
       </c>
       <c r="B2" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,28 +703,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bastfallet, 500m SSO, skogsväg, Gstr</t>
+          <t>Bastfallet, 500m SSO, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621132.5373988484</v>
+        <v>621028</v>
       </c>
       <c r="R2" t="n">
-        <v>6705707.332295355</v>
+        <v>6705698</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,34 +738,14 @@
           <t>Hedesunda</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>XG-Gäv-0536</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1993-08-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1993-08-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>10 ST. SKOGSKLOCKOR. Inventerat av Birger och Gun Jonsson.</t>
+          <t>2004-07-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,13 +754,17 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>KULTURMARK, VÄGKANT MOT TOMT/ÄNGSMARK, FRISK MORÄN ÖPPET.</t>
+          <t>Kulturmark, Skogsbryn/backkant mot åker, ohävdat men röjt</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 278216H</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +775,138 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Gun Jonsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>74250298</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>245</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bastfallet, 500m SSO, skogsväg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>621133</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6705707</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>XG-Gäv-0536</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2004-07-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2004-07-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>117 ex. Lokalen finns efter en skogsväg, SO bortom ett gult hus. På båda sidornaav vägen, på en sträcka av 100m. Inventerat av Birger och Gun Jonsson.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kulturmark, vägkant tillskogsväg, sly efter vägen</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Via Peter Ståhl</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 12338-2025 artfynd.xlsx
+++ b/artfynd/A 12338-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93943789</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,8 +921,17 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74250298</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>